--- a/data/ozon_new_products.xlsx
+++ b/data/ozon_new_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Новые товары Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новые товары Ozon'!$A$1:$Q$1</definedName>
@@ -563,14 +563,16 @@
       <c r="F2" t="n">
         <v>1900</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>8708409909</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.png?v=4beea95775</t>
+        </is>
+      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
